--- a/output/pdf_financials_xlsx/PNTR.xlsx
+++ b/output/pdf_financials_xlsx/PNTR.xlsx
@@ -4207,10 +4207,10 @@
         <v>2.002544</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.002544</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.01791</v>
       </c>
     </row>
     <row r="93">
@@ -7029,7 +7029,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7731,7 +7735,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PNTR.xlsx
+++ b/output/pdf_financials_xlsx/PNTR.xlsx
@@ -849,37 +849,37 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000172</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000135</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00013</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000207</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000325</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000563</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>9.2e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00058</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00314</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001003</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000929</v>
       </c>
     </row>
     <row r="13">
@@ -1497,37 +1497,37 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.469142</v>
+        <v>-0.469314</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.101185</v>
+        <v>-0.10132</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.097923</v>
+        <v>-0.098053</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.299387</v>
+        <v>-0.299594</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.391071</v>
+        <v>-0.391396</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.347674</v>
+        <v>-0.348237</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.347674</v>
+        <v>-0.347766</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.001273</v>
+        <v>-1.001853</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.001273</v>
+        <v>-1.004413</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.091351</v>
+        <v>-1.092354</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.091351</v>
+        <v>-1.09228</v>
       </c>
     </row>
     <row r="28">
@@ -1577,37 +1577,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.469142</v>
+        <v>-0.469314</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.101185</v>
+        <v>-0.10132</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.097923</v>
+        <v>-0.098053</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.299387</v>
+        <v>-0.299594</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.391071</v>
+        <v>-0.391396</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.347674</v>
+        <v>-0.348237</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.347674</v>
+        <v>-0.347766</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.001273</v>
+        <v>-1.001853</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.001273</v>
+        <v>-1.004413</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.091351</v>
+        <v>-1.092354</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.091351</v>
+        <v>-1.09228</v>
       </c>
     </row>
     <row r="30">
@@ -1788,22 +1788,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.018333</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001479</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001417</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.056337</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.023059</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.199301</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.199301</v>
@@ -1815,10 +1815,10 @@
         <v>0.095564</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.008227999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>3.079482</v>
       </c>
     </row>
     <row r="35">
@@ -1868,22 +1868,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.018333</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001479</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001417</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.056337</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.023059</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.199301</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.199301</v>
@@ -1895,10 +1895,10 @@
         <v>0.095564</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.008227999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>3.079482</v>
       </c>
     </row>
     <row r="37">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.035686</v>
+        <v>0.017353</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.001479</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001417</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.056337</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.023059</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2375,10 +2375,10 @@
         <v>1e-06</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.008229</v>
+        <v>1e-06</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.08338</v>
+        <v>0.003898</v>
       </c>
     </row>
     <row r="49">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">

--- a/output/pdf_financials_xlsx/PNTR.xlsx
+++ b/output/pdf_financials_xlsx/PNTR.xlsx
@@ -676,10 +676,10 @@
         <v>0.144582</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.106259</v>
+        <v>0.128259</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.229425</v>
+        <v>0.255425</v>
       </c>
     </row>
     <row r="8">
@@ -796,10 +796,10 @@
         <v>0.144582</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.106259</v>
+        <v>0.128259</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.229425</v>
+        <v>0.255425</v>
       </c>
     </row>
     <row r="11">
@@ -18184,7 +18184,11 @@
           <t>Director fees 7</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
